--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B747FB7D-2205-4531-A321-A8F10DA094C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815BC6DD-5D4B-4A43-BB22-049F527AFEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="2640" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -36,14 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="55">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Key</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="56">
   <si>
     <t>GpUp</t>
   </si>
@@ -115,10 +108,6 @@
   </si>
   <si>
     <t>GpLeftThumbLeft</t>
-  </si>
-  <si>
-    <t>Device</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>GamePad</t>
@@ -188,10 +177,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ActionKeyMaxCount</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>KeyID[0]</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -218,6 +203,21 @@
   <si>
     <t>ActionID</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DeviceKeyID</t>
+  </si>
+  <si>
+    <t>DeviceID</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>KeyID</t>
+  </si>
+  <si>
+    <t>Key</t>
   </si>
 </sst>
 </file>
@@ -561,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
@@ -569,290 +569,446 @@
     <col min="5" max="5" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2">
-        <v>-1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
-        <v>12</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="1">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
-        <v>14</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
-        <v>15</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="B23" s="1">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="1">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="1">
+        <v>23</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
-        <v>17</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <v>18</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <v>19</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <v>20</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
+      <c r="B26" s="1">
+        <v>24</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
         <v>23</v>
-      </c>
-      <c r="B24" s="1">
-        <v>21</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1">
-        <v>22</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1">
-        <v>23</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62AA4DB-6C78-44DC-A30A-4C66BF09A693}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -886,404 +1042,398 @@
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I2" s="2">
         <f>VLOOKUP(C2,KeyCode!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
         <f>VLOOKUP(D2,KeyCode!A:B,2,FALSE)</f>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2">
         <f>VLOOKUP(E2,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
         <f>VLOOKUP(F2,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2">
         <f>VLOOKUP(G2,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2">
         <f>VLOOKUP(H2,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
-      </c>
-      <c r="O2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP(C3,KeyCode!A:B,2,FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP(D3,KeyCode!A:B,2,FALSE)</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K3" s="2">
         <f>VLOOKUP(E3,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2">
         <f>VLOOKUP(F2,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2">
         <f>VLOOKUP(G2,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2">
         <f>VLOOKUP(H2,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP(C4,KeyCode!A:B,2,FALSE)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP(D4,KeyCode!A:B,2,FALSE)</f>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K4" s="2">
         <f>VLOOKUP(E4,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2">
         <f>VLOOKUP(F3,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2">
         <f>VLOOKUP(G3,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
         <f>VLOOKUP(H3,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP(C5,KeyCode!A:B,2,FALSE)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP(D5,KeyCode!A:B,2,FALSE)</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2">
         <f>VLOOKUP(E5,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2">
         <f>VLOOKUP(F4,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2">
         <f>VLOOKUP(G4,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2">
         <f>VLOOKUP(H4,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP(C6,KeyCode!A:B,2,FALSE)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP(D6,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2">
         <f>VLOOKUP(E6,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2">
         <f>VLOOKUP(F5,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2">
         <f>VLOOKUP(G5,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2">
         <f>VLOOKUP(H5,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP(C7,KeyCode!A:B,2,FALSE)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP(D7,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2">
         <f>VLOOKUP(E7,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2">
         <f>VLOOKUP(F6,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2">
         <f>VLOOKUP(G6,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2">
         <f>VLOOKUP(H6,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP(C8,KeyCode!A:B,2,FALSE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP(D8,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2">
         <f>VLOOKUP(E8,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2">
         <f>VLOOKUP(F7,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2">
         <f>VLOOKUP(G7,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2">
         <f>VLOOKUP(H7,KeyCode!A:B,2,FALSE)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1306,27 +1456,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155B8502-092A-4FDA-8EF8-EB558747B523}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>43</v>
+      </c>
+      <c r="B1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815BC6DD-5D4B-4A43-BB22-049F527AFEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0A8297-AF41-470C-8B77-958DEEC13C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4380" yWindow="-13905" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
   <si>
     <t>GpUp</t>
   </si>
@@ -218,6 +221,35 @@
   </si>
   <si>
     <t>Key</t>
+  </si>
+  <si>
+    <t>Move</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SelectMove</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GpCross</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GpCross</t>
+  </si>
+  <si>
+    <t>DragonCall</t>
+  </si>
+  <si>
+    <t>Dash</t>
+  </si>
+  <si>
+    <t>Parry</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -275,12 +307,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -561,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
@@ -1009,6 +1044,23 @@
       </c>
       <c r="E26" s="1">
         <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1074,7 @@
           <x14:formula1>
             <xm:f>Device!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C26</xm:sqref>
+          <xm:sqref>C2:C27</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1032,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62AA4DB-6C78-44DC-A30A-4C66BF09A693}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
@@ -1436,9 +1488,326 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="2">
+        <f>VLOOKUP(C9,KeyCode!A:B,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="J9" s="2">
+        <f>VLOOKUP(D9,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <f>VLOOKUP(E9,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <f>VLOOKUP(F8,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <f>VLOOKUP(G8,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <f>VLOOKUP(H8,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="2">
+        <f>VLOOKUP(C10,KeyCode!A:B,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="J10" s="2">
+        <f>VLOOKUP(D10,KeyCode!A:B,2,FALSE)</f>
+        <v>25</v>
+      </c>
+      <c r="K10" s="2">
+        <f>VLOOKUP(E10,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <f>VLOOKUP(F9,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <f>VLOOKUP(G9,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <f>VLOOKUP(H9,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="2">
+        <f>VLOOKUP(C11,KeyCode!A:B,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="J11" s="2">
+        <f>VLOOKUP(D11,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <f>VLOOKUP(E11,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <f>VLOOKUP(F10,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <f>VLOOKUP(G10,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <f>VLOOKUP(H10,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="2">
+        <f>VLOOKUP(C12,KeyCode!A:B,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="J12" s="2">
+        <f>VLOOKUP(D12,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <f>VLOOKUP(E12,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <f>VLOOKUP(F11,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <f>VLOOKUP(G11,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <f>VLOOKUP(H11,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="2">
+        <f>VLOOKUP(C13,KeyCode!A:B,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="J13" s="2">
+        <f>VLOOKUP(D13,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <f>VLOOKUP(E13,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <f>VLOOKUP(F12,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <f>VLOOKUP(G12,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <f>VLOOKUP(H12,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="2">
+        <f>VLOOKUP(C14,KeyCode!A:B,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="J14" s="2">
+        <f>VLOOKUP(D14,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <f>VLOOKUP(E14,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <f>VLOOKUP(F13,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <f>VLOOKUP(G13,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <f>VLOOKUP(H13,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -1446,7 +1815,7 @@
           <x14:formula1>
             <xm:f>KeyCode!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:H8</xm:sqref>
+          <xm:sqref>C2:H15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0A8297-AF41-470C-8B77-958DEEC13C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C99C9B3-1855-4964-B9E1-355255340256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="-13905" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7155" yWindow="2475" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="70">
   <si>
     <t>GpUp</t>
   </si>
@@ -249,6 +249,28 @@
   </si>
   <si>
     <t>Parry</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Start</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GpLeftVector</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GpRightVector</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GpLeftVector</t>
+  </si>
+  <si>
+    <t>GpRightVector</t>
+  </si>
+  <si>
+    <t>CursorMove</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -596,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
@@ -1061,6 +1083,40 @@
       </c>
       <c r="E27" s="1">
         <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="1">
+        <v>26</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="1">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1130,7 @@
           <x14:formula1>
             <xm:f>Device!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C27</xm:sqref>
+          <xm:sqref>C2:C29</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1084,10 +1140,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62AA4DB-6C78-44DC-A30A-4C66BF09A693}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.5" customWidth="1"/>
@@ -1493,10 +1549,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>42</v>
@@ -1515,7 +1571,7 @@
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP(C9,KeyCode!A:B,2,FALSE)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP(D9,KeyCode!A:B,2,FALSE)</f>
@@ -1543,13 +1599,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>42</v>
@@ -1565,26 +1621,26 @@
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP(C10,KeyCode!A:B,2,FALSE)</f>
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP(D10,KeyCode!A:B,2,FALSE)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2">
         <f>VLOOKUP(E10,KeyCode!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="L10" s="2">
-        <f>VLOOKUP(F9,KeyCode!A:B,2,FALSE)</f>
+        <f>VLOOKUP(F8,KeyCode!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <f>VLOOKUP(G9,KeyCode!A:B,2,FALSE)</f>
+        <f>VLOOKUP(G8,KeyCode!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
       <c r="N10" s="2">
-        <f>VLOOKUP(H9,KeyCode!A:B,2,FALSE)</f>
+        <f>VLOOKUP(H8,KeyCode!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1593,13 +1649,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>42</v>
@@ -1615,11 +1671,11 @@
       </c>
       <c r="I11" s="2">
         <f>VLOOKUP(C11,KeyCode!A:B,2,FALSE)</f>
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J11" s="2">
         <f>VLOOKUP(D11,KeyCode!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K11" s="2">
         <f>VLOOKUP(E11,KeyCode!A:B,2,FALSE)</f>
@@ -1642,11 +1698,11 @@
       <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>61</v>
+      <c r="B12" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>42</v>
@@ -1665,7 +1721,7 @@
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP(C12,KeyCode!A:B,2,FALSE)</f>
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP(D12,KeyCode!A:B,2,FALSE)</f>
@@ -1693,10 +1749,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>42</v>
@@ -1715,7 +1771,7 @@
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP(C13,KeyCode!A:B,2,FALSE)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP(D13,KeyCode!A:B,2,FALSE)</f>
@@ -1743,10 +1799,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>42</v>
@@ -1765,7 +1821,7 @@
       </c>
       <c r="I14" s="2">
         <f>VLOOKUP(C14,KeyCode!A:B,2,FALSE)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" s="2">
         <f>VLOOKUP(D14,KeyCode!A:B,2,FALSE)</f>
@@ -1789,20 +1845,104 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="2">
+        <f>VLOOKUP(C15,KeyCode!A:B,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="J15" s="2">
+        <f>VLOOKUP(D15,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <f>VLOOKUP(E15,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <f>VLOOKUP(F14,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <f>VLOOKUP(G14,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <f>VLOOKUP(H14,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="2">
+        <f>VLOOKUP(C16,KeyCode!A:B,2,FALSE)</f>
+        <v>25</v>
+      </c>
+      <c r="J16" s="2">
+        <f>VLOOKUP(D16,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <f>VLOOKUP(E16,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
+        <f>VLOOKUP(F15,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <f>VLOOKUP(G15,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <f>VLOOKUP(H15,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1815,7 +1955,7 @@
           <x14:formula1>
             <xm:f>KeyCode!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:H15</xm:sqref>
+          <xm:sqref>C2:H16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C99C9B3-1855-4964-B9E1-355255340256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A1450-46E1-44BC-B2E2-BFA0994C8FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7155" yWindow="2475" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KeyCode" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="71">
   <si>
     <t>GpUp</t>
   </si>
@@ -271,6 +271,10 @@
   </si>
   <si>
     <t>CursorMove</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ItemCursorMove</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1140,10 +1144,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62AA4DB-6C78-44DC-A30A-4C66BF09A693}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.5" customWidth="1"/>
@@ -1941,6 +1945,56 @@
       </c>
       <c r="N16" s="2">
         <f>VLOOKUP(H15,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="2">
+        <f>VLOOKUP(C17,KeyCode!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <f>VLOOKUP(D17,KeyCode!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="K17" s="2">
+        <f>VLOOKUP(E17,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="2">
+        <f>VLOOKUP(F16,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <f>VLOOKUP(G16,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <f>VLOOKUP(H16,KeyCode!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -1955,7 +2009,7 @@
           <x14:formula1>
             <xm:f>KeyCode!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:H16</xm:sqref>
+          <xm:sqref>C2:H17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/DXLibProject_Start/Data/CSV/KeyCode.xlsx
+++ b/DXLibProject_Start/Data/CSV/KeyCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98A1450-46E1-44BC-B2E2-BFA0994C8FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7652614-DAC1-4B74-AF77-70E15347FE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="72">
   <si>
     <t>GpUp</t>
   </si>
@@ -275,6 +275,10 @@
   </si>
   <si>
     <t>ItemCursorMove</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UseItem</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1144,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62AA4DB-6C78-44DC-A30A-4C66BF09A693}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
@@ -1998,6 +2002,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="2">
+        <f>VLOOKUP(C18,KeyCode!A:B,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="J18" s="2">
+        <f>VLOOKUP(D18,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <f>VLOOKUP(E18,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <f>VLOOKUP(F17,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <f>VLOOKUP(G17,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <f>VLOOKUP(H17,KeyCode!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2009,7 +2063,7 @@
           <x14:formula1>
             <xm:f>KeyCode!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:H17</xm:sqref>
+          <xm:sqref>C2:H18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
